--- a/data/source/2026-08/1С-Обороты-счета-57-август-2026.xlsx
+++ b/data/source/2026-08/1С-Обороты-счета-57-август-2026.xlsx
@@ -528,10 +528,10 @@
         <v>22798514</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>153682354</v>
+        <v>153883354</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>153295343.14</v>
+        <v>153496343.14</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>13523.7</v>
@@ -540,7 +540,7 @@
         <v>373487.16</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>-37173831</v>
+        <v>-37374831</v>
       </c>
       <c r="M8" s="16" t="e"/>
     </row>
@@ -558,12 +558,16 @@
         <v>12191119</v>
       </c>
       <c r="G9" s="21" t="e"/>
-      <c r="H9" s="19" t="e"/>
-      <c r="I9" s="21" t="e"/>
+      <c r="H9" s="20" t="n">
+        <v>201000</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>201000</v>
+      </c>
       <c r="J9" s="21" t="e"/>
       <c r="K9" s="21" t="e"/>
       <c r="L9" s="20" t="n">
-        <v>12191119</v>
+        <v>11990119</v>
       </c>
       <c r="M9" s="19" t="e"/>
     </row>
@@ -658,10 +662,10 @@
         <v>22798514</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>153682354</v>
+        <v>153883354</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>153295343.14</v>
+        <v>153496343.14</v>
       </c>
       <c r="J12" s="25" t="n">
         <v>13523.7</v>
@@ -671,7 +675,7 @@
       </c>
       <c r="L12" s="26" t="e"/>
       <c r="M12" s="25" t="n">
-        <v>37173831</v>
+        <v>37374831</v>
       </c>
     </row>
   </sheetData>
